--- a/data/cinema.xlsx
+++ b/data/cinema.xlsx
@@ -77,7 +77,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>2026-10-08 11:35:57</t>
+    <t>2026-10-09 23:34:45</t>
   </si>
   <si>
     <t>2</t>
@@ -650,6 +650,9 @@
     <t>121.3687770</t>
   </si>
   <si>
+    <t>2026-10-09 23:34:46</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
@@ -1073,9 +1076,6 @@
     <t>120.9658740</t>
   </si>
   <si>
-    <t>2026-10-08 11:35:58</t>
-  </si>
-  <si>
     <t>51</t>
   </si>
   <si>
@@ -1103,9 +1103,6 @@
     <t>百老匯影城竹北店</t>
   </si>
   <si>
-    <t>HSINCHU_COUNTY</t>
-  </si>
-  <si>
     <t>新竹縣竹北市自強南路36號3~5樓</t>
   </si>
   <si>
@@ -1517,6 +1514,9 @@
     <t>https://www.cm-movie.com.tw/category/time/</t>
   </si>
   <si>
+    <t>2026-10-09 23:34:47</t>
+  </si>
+  <si>
     <t>73</t>
   </si>
   <si>
@@ -2189,7 +2189,7 @@
     <t>台東秀泰影城</t>
   </si>
   <si>
-    <t>UNKNOWN</t>
+    <t>TAITUNG</t>
   </si>
   <si>
     <t>台東市鐵花里5鄰新生路93號</t>
@@ -3473,33 +3473,33 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L30" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>82</v>
@@ -3511,36 +3511,36 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>20</v>
@@ -3549,36 +3549,36 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>20</v>
@@ -3587,33 +3587,33 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>82</v>
@@ -3625,36 +3625,36 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>20</v>
@@ -3663,36 +3663,36 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L35" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>20</v>
@@ -3701,36 +3701,36 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L36" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E37" t="s" s="0">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>20</v>
@@ -3739,36 +3739,36 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L37" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E38" t="s" s="0">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>20</v>
@@ -3777,36 +3777,36 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L38" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>182</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I39" t="s" s="0">
         <v>20</v>
@@ -3815,36 +3815,36 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L39" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>15</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I40" t="s" s="0">
         <v>20</v>
@@ -3853,33 +3853,33 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H41" t="s" s="0">
         <v>171</v>
@@ -3891,36 +3891,36 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L41" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I42" t="s" s="0">
         <v>20</v>
@@ -3929,36 +3929,36 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L42" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F43" t="s" s="0">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I43" t="s" s="0">
         <v>20</v>
@@ -3967,33 +3967,33 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L43" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F44" t="s" s="0">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H44" t="s" s="0">
         <v>82</v>
@@ -4005,33 +4005,33 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L44" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E45" t="s" s="0">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F45" t="s" s="0">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H45" t="s" s="0">
         <v>19</v>
@@ -4043,36 +4043,36 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L45" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>20</v>
@@ -4081,33 +4081,33 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L46" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H47" t="s" s="0">
         <v>19</v>
@@ -4119,33 +4119,33 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H48" t="s" s="0">
         <v>96</v>
@@ -4157,36 +4157,36 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L48" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I49" t="s" s="0">
         <v>20</v>
@@ -4195,36 +4195,36 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L49" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I50" t="s" s="0">
         <v>20</v>
@@ -4233,33 +4233,33 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="L50" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H51" t="s" s="0">
         <v>19</v>
@@ -4271,10 +4271,10 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L51" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52">
@@ -4288,7 +4288,7 @@
         <v>356</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>357</v>
@@ -4309,10 +4309,10 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L52" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53">
@@ -4326,16 +4326,16 @@
         <v>362</v>
       </c>
       <c r="D53" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="E53" t="s" s="0">
         <v>363</v>
       </c>
-      <c r="E53" t="s" s="0">
+      <c r="F53" t="s" s="0">
         <v>364</v>
       </c>
-      <c r="F53" t="s" s="0">
+      <c r="G53" t="s" s="0">
         <v>365</v>
-      </c>
-      <c r="G53" t="s" s="0">
-        <v>366</v>
       </c>
       <c r="H53" t="s" s="0">
         <v>137</v>
@@ -4347,33 +4347,33 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B54" t="s" s="0">
         <v>367</v>
       </c>
-      <c r="B54" t="s" s="0">
+      <c r="C54" t="s" s="0">
         <v>368</v>
       </c>
-      <c r="C54" t="s" s="0">
+      <c r="D54" t="s" s="0">
         <v>369</v>
       </c>
-      <c r="D54" t="s" s="0">
+      <c r="E54" t="s" s="0">
         <v>370</v>
       </c>
-      <c r="E54" t="s" s="0">
+      <c r="F54" t="s" s="0">
         <v>371</v>
       </c>
-      <c r="F54" t="s" s="0">
+      <c r="G54" t="s" s="0">
         <v>372</v>
-      </c>
-      <c r="G54" t="s" s="0">
-        <v>373</v>
       </c>
       <c r="H54" t="s" s="0">
         <v>96</v>
@@ -4385,33 +4385,33 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L54" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="B55" t="s" s="0">
         <v>374</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="C55" t="s" s="0">
         <v>375</v>
       </c>
-      <c r="C55" t="s" s="0">
+      <c r="D55" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E55" t="s" s="0">
         <v>376</v>
       </c>
-      <c r="D55" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E55" t="s" s="0">
+      <c r="F55" t="s" s="0">
         <v>377</v>
       </c>
-      <c r="F55" t="s" s="0">
+      <c r="G55" t="s" s="0">
         <v>378</v>
-      </c>
-      <c r="G55" t="s" s="0">
-        <v>379</v>
       </c>
       <c r="H55" t="s" s="0">
         <v>19</v>
@@ -4423,33 +4423,33 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L55" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B56" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="C56" t="s" s="0">
         <v>381</v>
       </c>
-      <c r="C56" t="s" s="0">
+      <c r="D56" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E56" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="D56" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E56" t="s" s="0">
+      <c r="F56" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="F56" t="s" s="0">
+      <c r="G56" t="s" s="0">
         <v>384</v>
-      </c>
-      <c r="G56" t="s" s="0">
-        <v>385</v>
       </c>
       <c r="H56" t="s" s="0">
         <v>19</v>
@@ -4461,33 +4461,33 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="B57" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="C57" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="C57" t="s" s="0">
+      <c r="D57" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E57" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D57" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E57" t="s" s="0">
+      <c r="F57" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="F57" t="s" s="0">
+      <c r="G57" t="s" s="0">
         <v>390</v>
-      </c>
-      <c r="G57" t="s" s="0">
-        <v>391</v>
       </c>
       <c r="H57" t="s" s="0">
         <v>19</v>
@@ -4499,37 +4499,37 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L57" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
+        <v>391</v>
+      </c>
+      <c r="B58" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="C58" t="s" s="0">
         <v>393</v>
       </c>
-      <c r="C58" t="s" s="0">
+      <c r="D58" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E58" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="D58" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E58" t="s" s="0">
+      <c r="F58" t="s" s="0">
         <v>395</v>
       </c>
-      <c r="F58" t="s" s="0">
+      <c r="G58" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="G58" t="s" s="0">
+      <c r="H58" t="s" s="0">
         <v>397</v>
       </c>
-      <c r="H58" t="s" s="0">
-        <v>398</v>
-      </c>
       <c r="I58" t="s" s="0">
         <v>20</v>
       </c>
@@ -4537,37 +4537,37 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L58" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="B59" t="s" s="0">
         <v>399</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="C59" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="C59" t="s" s="0">
+      <c r="D59" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E59" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="D59" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E59" t="s" s="0">
+      <c r="F59" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="F59" t="s" s="0">
+      <c r="G59" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="G59" t="s" s="0">
+      <c r="H59" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="H59" t="s" s="0">
-        <v>405</v>
-      </c>
       <c r="I59" t="s" s="0">
         <v>20</v>
       </c>
@@ -4575,37 +4575,37 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L59" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B60" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="C60" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="C60" t="s" s="0">
+      <c r="D60" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E60" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="D60" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E60" t="s" s="0">
+      <c r="F60" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F60" t="s" s="0">
+      <c r="G60" t="s" s="0">
         <v>410</v>
       </c>
-      <c r="G60" t="s" s="0">
+      <c r="H60" t="s" s="0">
         <v>411</v>
       </c>
-      <c r="H60" t="s" s="0">
-        <v>412</v>
-      </c>
       <c r="I60" t="s" s="0">
         <v>20</v>
       </c>
@@ -4613,37 +4613,37 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L60" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="B61" t="s" s="0">
         <v>413</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="C61" t="s" s="0">
         <v>414</v>
       </c>
-      <c r="C61" t="s" s="0">
+      <c r="D61" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E61" t="s" s="0">
         <v>415</v>
       </c>
-      <c r="D61" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E61" t="s" s="0">
+      <c r="F61" t="s" s="0">
         <v>416</v>
       </c>
-      <c r="F61" t="s" s="0">
+      <c r="G61" t="s" s="0">
         <v>417</v>
       </c>
-      <c r="G61" t="s" s="0">
+      <c r="H61" t="s" s="0">
         <v>418</v>
       </c>
-      <c r="H61" t="s" s="0">
-        <v>419</v>
-      </c>
       <c r="I61" t="s" s="0">
         <v>20</v>
       </c>
@@ -4651,37 +4651,37 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="B62" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="C62" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C62" t="s" s="0">
+      <c r="D62" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E62" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="D62" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E62" t="s" s="0">
+      <c r="F62" t="s" s="0">
         <v>423</v>
       </c>
-      <c r="F62" t="s" s="0">
+      <c r="G62" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="G62" t="s" s="0">
+      <c r="H62" t="s" s="0">
         <v>425</v>
       </c>
-      <c r="H62" t="s" s="0">
-        <v>426</v>
-      </c>
       <c r="I62" t="s" s="0">
         <v>20</v>
       </c>
@@ -4689,37 +4689,37 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L62" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
+        <v>426</v>
+      </c>
+      <c r="B63" t="s" s="0">
         <v>427</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="C63" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="C63" t="s" s="0">
+      <c r="D63" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E63" t="s" s="0">
         <v>429</v>
       </c>
-      <c r="D63" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E63" t="s" s="0">
+      <c r="F63" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="F63" t="s" s="0">
+      <c r="G63" t="s" s="0">
         <v>431</v>
       </c>
-      <c r="G63" t="s" s="0">
+      <c r="H63" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="H63" t="s" s="0">
-        <v>433</v>
-      </c>
       <c r="I63" t="s" s="0">
         <v>20</v>
       </c>
@@ -4727,37 +4727,37 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L63" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
+        <v>433</v>
+      </c>
+      <c r="B64" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="C64" t="s" s="0">
         <v>435</v>
       </c>
-      <c r="C64" t="s" s="0">
+      <c r="D64" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E64" t="s" s="0">
         <v>436</v>
       </c>
-      <c r="D64" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E64" t="s" s="0">
+      <c r="F64" t="s" s="0">
         <v>437</v>
       </c>
-      <c r="F64" t="s" s="0">
+      <c r="G64" t="s" s="0">
         <v>438</v>
       </c>
-      <c r="G64" t="s" s="0">
+      <c r="H64" t="s" s="0">
         <v>439</v>
       </c>
-      <c r="H64" t="s" s="0">
-        <v>440</v>
-      </c>
       <c r="I64" t="s" s="0">
         <v>20</v>
       </c>
@@ -4765,37 +4765,37 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L64" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
+        <v>440</v>
+      </c>
+      <c r="B65" t="s" s="0">
         <v>441</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="C65" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="C65" t="s" s="0">
+      <c r="D65" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E65" t="s" s="0">
         <v>443</v>
       </c>
-      <c r="D65" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E65" t="s" s="0">
+      <c r="F65" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="F65" t="s" s="0">
+      <c r="G65" t="s" s="0">
         <v>445</v>
       </c>
-      <c r="G65" t="s" s="0">
+      <c r="H65" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="H65" t="s" s="0">
-        <v>447</v>
-      </c>
       <c r="I65" t="s" s="0">
         <v>20</v>
       </c>
@@ -4803,37 +4803,37 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L65" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
+        <v>447</v>
+      </c>
+      <c r="B66" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="C66" t="s" s="0">
         <v>449</v>
       </c>
-      <c r="C66" t="s" s="0">
+      <c r="D66" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E66" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="D66" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E66" t="s" s="0">
+      <c r="F66" t="s" s="0">
         <v>451</v>
       </c>
-      <c r="F66" t="s" s="0">
+      <c r="G66" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="G66" t="s" s="0">
+      <c r="H66" t="s" s="0">
         <v>453</v>
       </c>
-      <c r="H66" t="s" s="0">
-        <v>454</v>
-      </c>
       <c r="I66" t="s" s="0">
         <v>20</v>
       </c>
@@ -4841,37 +4841,37 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L66" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
+        <v>454</v>
+      </c>
+      <c r="B67" t="s" s="0">
         <v>455</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="C67" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="C67" t="s" s="0">
+      <c r="D67" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="E67" t="s" s="0">
         <v>457</v>
       </c>
-      <c r="D67" t="s" s="0">
-        <v>370</v>
-      </c>
-      <c r="E67" t="s" s="0">
+      <c r="F67" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="F67" t="s" s="0">
+      <c r="G67" t="s" s="0">
         <v>459</v>
       </c>
-      <c r="G67" t="s" s="0">
+      <c r="H67" t="s" s="0">
         <v>460</v>
       </c>
-      <c r="H67" t="s" s="0">
-        <v>461</v>
-      </c>
       <c r="I67" t="s" s="0">
         <v>20</v>
       </c>
@@ -4879,33 +4879,33 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L67" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
+        <v>461</v>
+      </c>
+      <c r="B68" t="s" s="0">
         <v>462</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="C68" t="s" s="0">
         <v>463</v>
       </c>
-      <c r="C68" t="s" s="0">
+      <c r="D68" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="D68" t="s" s="0">
+      <c r="E68" t="s" s="0">
         <v>465</v>
       </c>
-      <c r="E68" t="s" s="0">
+      <c r="F68" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="F68" t="s" s="0">
+      <c r="G68" t="s" s="0">
         <v>467</v>
-      </c>
-      <c r="G68" t="s" s="0">
-        <v>468</v>
       </c>
       <c r="H68" t="s" s="0">
         <v>96</v>
@@ -4917,33 +4917,33 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L68" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
+        <v>468</v>
+      </c>
+      <c r="B69" t="s" s="0">
         <v>469</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="C69" t="s" s="0">
         <v>470</v>
       </c>
-      <c r="C69" t="s" s="0">
+      <c r="D69" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E69" t="s" s="0">
         <v>471</v>
       </c>
-      <c r="D69" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E69" t="s" s="0">
+      <c r="F69" t="s" s="0">
         <v>472</v>
       </c>
-      <c r="F69" t="s" s="0">
+      <c r="G69" t="s" s="0">
         <v>473</v>
-      </c>
-      <c r="G69" t="s" s="0">
-        <v>474</v>
       </c>
       <c r="H69" t="s" s="0">
         <v>19</v>
@@ -4955,33 +4955,33 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L69" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
+        <v>474</v>
+      </c>
+      <c r="B70" t="s" s="0">
         <v>475</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="C70" t="s" s="0">
         <v>476</v>
       </c>
-      <c r="C70" t="s" s="0">
+      <c r="D70" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E70" t="s" s="0">
         <v>477</v>
       </c>
-      <c r="D70" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E70" t="s" s="0">
+      <c r="F70" t="s" s="0">
         <v>478</v>
       </c>
-      <c r="F70" t="s" s="0">
+      <c r="G70" t="s" s="0">
         <v>479</v>
-      </c>
-      <c r="G70" t="s" s="0">
-        <v>480</v>
       </c>
       <c r="H70" t="s" s="0">
         <v>19</v>
@@ -4993,33 +4993,33 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L70" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
+        <v>480</v>
+      </c>
+      <c r="B71" t="s" s="0">
         <v>481</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="C71" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="C71" t="s" s="0">
+      <c r="D71" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E71" t="s" s="0">
         <v>483</v>
       </c>
-      <c r="D71" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E71" t="s" s="0">
+      <c r="F71" t="s" s="0">
         <v>484</v>
       </c>
-      <c r="F71" t="s" s="0">
+      <c r="G71" t="s" s="0">
         <v>485</v>
-      </c>
-      <c r="G71" t="s" s="0">
-        <v>486</v>
       </c>
       <c r="H71" t="s" s="0">
         <v>19</v>
@@ -5031,37 +5031,37 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L71" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
+        <v>486</v>
+      </c>
+      <c r="B72" t="s" s="0">
         <v>487</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="C72" t="s" s="0">
         <v>488</v>
       </c>
-      <c r="C72" t="s" s="0">
+      <c r="D72" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E72" t="s" s="0">
         <v>489</v>
       </c>
-      <c r="D72" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E72" t="s" s="0">
+      <c r="F72" t="s" s="0">
         <v>490</v>
       </c>
-      <c r="F72" t="s" s="0">
+      <c r="G72" t="s" s="0">
         <v>491</v>
       </c>
-      <c r="G72" t="s" s="0">
+      <c r="H72" t="s" s="0">
         <v>492</v>
       </c>
-      <c r="H72" t="s" s="0">
-        <v>493</v>
-      </c>
       <c r="I72" t="s" s="0">
         <v>20</v>
       </c>
@@ -5069,37 +5069,37 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="L72" t="s" s="0">
-        <v>353</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
+        <v>493</v>
+      </c>
+      <c r="B73" t="s" s="0">
         <v>494</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="C73" t="s" s="0">
         <v>495</v>
       </c>
-      <c r="C73" t="s" s="0">
+      <c r="D73" t="s" s="0">
+        <v>464</v>
+      </c>
+      <c r="E73" t="s" s="0">
         <v>496</v>
       </c>
-      <c r="D73" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="E73" t="s" s="0">
+      <c r="F73" t="s" s="0">
         <v>497</v>
       </c>
-      <c r="F73" t="s" s="0">
+      <c r="G73" t="s" s="0">
         <v>498</v>
       </c>
-      <c r="G73" t="s" s="0">
+      <c r="H73" t="s" s="0">
         <v>499</v>
       </c>
-      <c r="H73" t="s" s="0">
-        <v>500</v>
-      </c>
       <c r="I73" t="s" s="0">
         <v>20</v>
       </c>
@@ -5107,10 +5107,10 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L73" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -5124,7 +5124,7 @@
         <v>503</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>504</v>
@@ -5145,10 +5145,10 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L74" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75">
@@ -5162,7 +5162,7 @@
         <v>510</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>511</v>
@@ -5183,10 +5183,10 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L75" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76">
@@ -5221,10 +5221,10 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L76" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77">
@@ -5259,10 +5259,10 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L77" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78">
@@ -5297,10 +5297,10 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L78" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79">
@@ -5335,10 +5335,10 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L79" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80">
@@ -5373,10 +5373,10 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L80" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81">
@@ -5411,10 +5411,10 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L81" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="82">
@@ -5449,10 +5449,10 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L82" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="83">
@@ -5487,10 +5487,10 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L83" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84">
@@ -5525,10 +5525,10 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L84" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85">
@@ -5563,10 +5563,10 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L85" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="86">
@@ -5601,10 +5601,10 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L86" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87">
@@ -5639,10 +5639,10 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L87" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88">
@@ -5677,10 +5677,10 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L88" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89">
@@ -5715,10 +5715,10 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L89" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90">
@@ -5753,10 +5753,10 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L90" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91">
@@ -5791,10 +5791,10 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L91" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="92">
@@ -5829,10 +5829,10 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L92" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
@@ -5867,10 +5867,10 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L93" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94">
@@ -5905,10 +5905,10 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L94" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95">
@@ -5943,10 +5943,10 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L95" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96">
@@ -5981,10 +5981,10 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L96" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97">
@@ -6019,10 +6019,10 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L97" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98">
@@ -6057,10 +6057,10 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L98" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="99">
@@ -6095,10 +6095,10 @@
         <v>20</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L99" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100">
@@ -6133,10 +6133,10 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L100" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101">
@@ -6171,10 +6171,10 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L101" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102">
@@ -6209,10 +6209,10 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L102" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103">
@@ -6247,10 +6247,10 @@
         <v>20</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L103" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104">
@@ -6285,10 +6285,10 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L104" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105">
@@ -6323,10 +6323,10 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L105" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106">
@@ -6361,10 +6361,10 @@
         <v>20</v>
       </c>
       <c r="K106" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L106" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107">
@@ -6399,10 +6399,10 @@
         <v>20</v>
       </c>
       <c r="K107" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L107" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="108">
@@ -6437,10 +6437,10 @@
         <v>20</v>
       </c>
       <c r="K108" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L108" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109">
@@ -6475,10 +6475,10 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
       <c r="L109" t="s" s="0">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/data/cinema.xlsx
+++ b/data/cinema.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="871">
   <si>
     <t>cinemaId</t>
   </si>
@@ -20,6 +20,9 @@
     <t>sourceId</t>
   </si>
   <si>
+    <t>sourceUrl</t>
+  </si>
+  <si>
     <t>cinemaName</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>t02a01</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a01/a02/</t>
+  </si>
+  <si>
     <t>台北信義威秀</t>
   </si>
   <si>
@@ -80,12 +86,18 @@
     <t>2026-10-09 23:34:45</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:37</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>t02a11</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a11/a02/</t>
+  </si>
+  <si>
     <t>MUVIE CINEMAS台北松仁威秀</t>
   </si>
   <si>
@@ -104,6 +116,9 @@
     <t>t02a12</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a12/a02/</t>
+  </si>
+  <si>
     <t>台北南港LaLaport威秀影城</t>
   </si>
   <si>
@@ -122,6 +137,9 @@
     <t>t02a09</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a09/a02/</t>
+  </si>
+  <si>
     <t>喜樂時代影城</t>
   </si>
   <si>
@@ -143,6 +161,9 @@
     <t>t02a03</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a03/a02/</t>
+  </si>
+  <si>
     <t>微風影城</t>
   </si>
   <si>
@@ -164,6 +185,9 @@
     <t>t02a08</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a08/a02/</t>
+  </si>
+  <si>
     <t>誠品電影院</t>
   </si>
   <si>
@@ -185,6 +209,9 @@
     <t>t02a05</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a05/a02/</t>
+  </si>
+  <si>
     <t>總督影城</t>
   </si>
   <si>
@@ -206,6 +233,9 @@
     <t>t02a13</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a13/a02/</t>
+  </si>
+  <si>
     <t>大巨蛋秀泰影城</t>
   </si>
   <si>
@@ -227,6 +257,9 @@
     <t>t02a06</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02a06/a02/</t>
+  </si>
+  <si>
     <t>哈拉影城</t>
   </si>
   <si>
@@ -248,6 +281,9 @@
     <t>t02b01</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b01/a02/</t>
+  </si>
+  <si>
     <t>國賓戲院</t>
   </si>
   <si>
@@ -269,6 +305,9 @@
     <t>t02b03</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b03/a02/</t>
+  </si>
+  <si>
     <t>樂聲影城</t>
   </si>
   <si>
@@ -290,6 +329,9 @@
     <t>t02b05</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b05/a02/</t>
+  </si>
+  <si>
     <t>台北新光影城</t>
   </si>
   <si>
@@ -311,6 +353,9 @@
     <t>t02b14</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b14/a02/</t>
+  </si>
+  <si>
     <t>台北京站威秀</t>
   </si>
   <si>
@@ -329,6 +374,9 @@
     <t>t02b07</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b07/a02/</t>
+  </si>
+  <si>
     <t>真善美戲院</t>
   </si>
   <si>
@@ -350,6 +398,9 @@
     <t>t02b06</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b06/a02/</t>
+  </si>
+  <si>
     <t>喜樂時代影城西門今日店</t>
   </si>
   <si>
@@ -371,6 +422,9 @@
     <t>t02b08</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b08/a02/</t>
+  </si>
+  <si>
     <t>台北西門威秀影城</t>
   </si>
   <si>
@@ -392,6 +446,9 @@
     <t>t02b16</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02b16/a02/</t>
+  </si>
+  <si>
     <t>光點華山電影館</t>
   </si>
   <si>
@@ -413,6 +470,9 @@
     <t>t02c01</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02c01/a02/</t>
+  </si>
+  <si>
     <t>百老匯影城公館店</t>
   </si>
   <si>
@@ -434,6 +494,9 @@
     <t>t02d05</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d05/a02/</t>
+  </si>
+  <si>
     <t>美麗華大直</t>
   </si>
   <si>
@@ -455,6 +518,9 @@
     <t>t02d04</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d04/a02/</t>
+  </si>
+  <si>
     <t>台北天母新光影城</t>
   </si>
   <si>
@@ -470,12 +536,18 @@
     <t>https://www.skcinemas.com/sessions?c=1005</t>
   </si>
   <si>
+    <t>2026-10-20 16:15:38</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
     <t>t02d03</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d03/a02/</t>
+  </si>
+  <si>
     <t>欣欣秀泰影城</t>
   </si>
   <si>
@@ -497,6 +569,9 @@
     <t>t02d02</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d02/a02/</t>
+  </si>
+  <si>
     <t>國賓長春影城</t>
   </si>
   <si>
@@ -515,6 +590,9 @@
     <t>t02d06</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d06/a02/</t>
+  </si>
+  <si>
     <t>美麗新大直皇家影城</t>
   </si>
   <si>
@@ -536,6 +614,9 @@
     <t>t02d20</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02d20/a02/</t>
+  </si>
+  <si>
     <t>光點台北電影院</t>
   </si>
   <si>
@@ -557,6 +638,9 @@
     <t>t02e07</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e07/a02/</t>
+  </si>
+  <si>
     <t>板橋大遠百威秀影城</t>
   </si>
   <si>
@@ -578,6 +662,9 @@
     <t>t02e12</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e12/a02/</t>
+  </si>
+  <si>
     <t>林口三井OUTLET威秀影城</t>
   </si>
   <si>
@@ -596,6 +683,9 @@
     <t>t02e03</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e03/a02/</t>
+  </si>
+  <si>
     <t>新莊鴻金寶麻吉影城</t>
   </si>
   <si>
@@ -617,6 +707,9 @@
     <t>t02e04</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e04/a02/</t>
+  </si>
+  <si>
     <t>三重天台戲院</t>
   </si>
   <si>
@@ -638,6 +731,9 @@
     <t>t02e10</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e10/a02/</t>
+  </si>
+  <si>
     <t>國賓林口昕境廣場</t>
   </si>
   <si>
@@ -659,6 +755,9 @@
     <t>t02e11</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e11/a02/</t>
+  </si>
+  <si>
     <t>國賓新莊晶冠廣場影城</t>
   </si>
   <si>
@@ -677,6 +776,9 @@
     <t>t02e13</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e13/a02/</t>
+  </si>
+  <si>
     <t>樹林秀泰影城</t>
   </si>
   <si>
@@ -698,6 +800,9 @@
     <t>t02e15</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e15/a02/</t>
+  </si>
+  <si>
     <t>土城秀泰影城</t>
   </si>
   <si>
@@ -719,6 +824,9 @@
     <t>t02e18</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e18/a02/</t>
+  </si>
+  <si>
     <t>國賓影城淡水禮萊廣場</t>
   </si>
   <si>
@@ -737,6 +845,9 @@
     <t>t02e17</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e17/a02/</t>
+  </si>
+  <si>
     <t>永和喜樂時代影城</t>
   </si>
   <si>
@@ -758,6 +869,9 @@
     <t>t02e20</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e20/a02/</t>
+  </si>
+  <si>
     <t>中和環球威秀影城</t>
   </si>
   <si>
@@ -779,6 +893,9 @@
     <t>t02e21</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e21/a02/</t>
+  </si>
+  <si>
     <t>新店裕隆城威秀影城</t>
   </si>
   <si>
@@ -800,6 +917,9 @@
     <t>t02e08</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e08/a02/</t>
+  </si>
+  <si>
     <t>府中15</t>
   </si>
   <si>
@@ -821,6 +941,9 @@
     <t>t02e22</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02e22/a02/</t>
+  </si>
+  <si>
     <t>國家電影及視聽文化中心</t>
   </si>
   <si>
@@ -842,6 +965,9 @@
     <t>t02f05</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02f05/a02/</t>
+  </si>
+  <si>
     <t>景美佳佳戲院</t>
   </si>
   <si>
@@ -863,6 +989,9 @@
     <t>t03301</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03301/a03/</t>
+  </si>
+  <si>
     <t>美麗新台茂影城</t>
   </si>
   <si>
@@ -884,6 +1013,9 @@
     <t>t03302</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03302/a03/</t>
+  </si>
+  <si>
     <t>星橋國際影城</t>
   </si>
   <si>
@@ -905,6 +1037,9 @@
     <t>t03303</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03303/a03/</t>
+  </si>
+  <si>
     <t>威尼斯影城</t>
   </si>
   <si>
@@ -926,6 +1061,9 @@
     <t>t03304</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03304/a03/</t>
+  </si>
+  <si>
     <t>國賓桃園八德</t>
   </si>
   <si>
@@ -944,6 +1082,9 @@
     <t>t03308</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03308/a03/</t>
+  </si>
+  <si>
     <t>桃園統領威秀影城</t>
   </si>
   <si>
@@ -962,6 +1103,9 @@
     <t>t03307</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03307/a03/</t>
+  </si>
+  <si>
     <t>桃園站前in89豪華影城</t>
   </si>
   <si>
@@ -983,6 +1127,9 @@
     <t>t03317</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03317/a03/</t>
+  </si>
+  <si>
     <t>桃園桃知道威秀影城</t>
   </si>
   <si>
@@ -1001,6 +1148,9 @@
     <t>t03315</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03315/a03/</t>
+  </si>
+  <si>
     <t>桃園新光影城</t>
   </si>
   <si>
@@ -1019,6 +1169,9 @@
     <t>t03311</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03311/a03/</t>
+  </si>
+  <si>
     <t>桃園光影文化館</t>
   </si>
   <si>
@@ -1040,6 +1193,9 @@
     <t>t03312</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03312/a03/</t>
+  </si>
+  <si>
     <t>中壢光影電影館</t>
   </si>
   <si>
@@ -1061,6 +1217,9 @@
     <t>t03505</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03505/a35/</t>
+  </si>
+  <si>
     <t>新竹大遠百威秀影城</t>
   </si>
   <si>
@@ -1082,6 +1241,9 @@
     <t>t03508</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03508/a35/</t>
+  </si>
+  <si>
     <t>新竹巨城威秀影城</t>
   </si>
   <si>
@@ -1100,6 +1262,9 @@
     <t>t03510</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03510/a35/</t>
+  </si>
+  <si>
     <t>百老匯影城竹北店</t>
   </si>
   <si>
@@ -1118,6 +1283,9 @@
     <t>t04401</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04401/a04/</t>
+  </si>
+  <si>
     <t>台中新光影城</t>
   </si>
   <si>
@@ -1139,6 +1307,9 @@
     <t>t04402</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04402/a04/</t>
+  </si>
+  <si>
     <t>台中老虎城威秀</t>
   </si>
   <si>
@@ -1157,6 +1328,9 @@
     <t>t04407</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04407/a04/</t>
+  </si>
+  <si>
     <t>台中大遠百威秀影城</t>
   </si>
   <si>
@@ -1175,6 +1349,9 @@
     <t>t04409</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04409/a04/</t>
+  </si>
+  <si>
     <t>台中iFG遠雄廣場威秀影城</t>
   </si>
   <si>
@@ -1193,6 +1370,9 @@
     <t>t04404</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04404/a04/</t>
+  </si>
+  <si>
     <t>日日新影城</t>
   </si>
   <si>
@@ -1214,6 +1394,9 @@
     <t>t04405</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04405/a04/</t>
+  </si>
+  <si>
     <t>親親戲院</t>
   </si>
   <si>
@@ -1235,6 +1418,9 @@
     <t>t04424</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04424/a04/</t>
+  </si>
+  <si>
     <t>全球影城</t>
   </si>
   <si>
@@ -1256,6 +1442,9 @@
     <t>t04410</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04410/a04/</t>
+  </si>
+  <si>
     <t>台中站前秀泰影城</t>
   </si>
   <si>
@@ -1277,6 +1466,9 @@
     <t>t04411</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04411/a04/</t>
+  </si>
+  <si>
     <t>台中文心秀泰影城</t>
   </si>
   <si>
@@ -1298,6 +1490,9 @@
     <t>t04412</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04412/a04/</t>
+  </si>
+  <si>
     <t>台中豐原in89豪華影城</t>
   </si>
   <si>
@@ -1319,6 +1514,9 @@
     <t>t04413</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04413/a04/</t>
+  </si>
+  <si>
     <t>台中麗寶秀泰</t>
   </si>
   <si>
@@ -1340,6 +1538,9 @@
     <t>t04426</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04426/a04/</t>
+  </si>
+  <si>
     <t>時代數位3D影城</t>
   </si>
   <si>
@@ -1361,6 +1562,9 @@
     <t>t04427</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04427/a04/</t>
+  </si>
+  <si>
     <t>中山73影視藝文空間</t>
   </si>
   <si>
@@ -1382,6 +1586,9 @@
     <t>t04428</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04428/a04/</t>
+  </si>
+  <si>
     <t>王牌映画影城</t>
   </si>
   <si>
@@ -1403,6 +1610,9 @@
     <t>t06607</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06607/a06/</t>
+  </si>
+  <si>
     <t>台南新光影城</t>
   </si>
   <si>
@@ -1424,6 +1634,9 @@
     <t>t06609</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06609/a06/</t>
+  </si>
+  <si>
     <t>台南大遠百威秀影城</t>
   </si>
   <si>
@@ -1442,6 +1655,9 @@
     <t>t06610</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06610/a06/</t>
+  </si>
+  <si>
     <t>台南南紡威秀影城</t>
   </si>
   <si>
@@ -1460,6 +1676,9 @@
     <t>t06611</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06611/a06/</t>
+  </si>
+  <si>
     <t>台南FOCUS威秀影城</t>
   </si>
   <si>
@@ -1478,6 +1697,9 @@
     <t>t06602</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06602/a06/</t>
+  </si>
+  <si>
     <t>南台電影城</t>
   </si>
   <si>
@@ -1499,6 +1721,9 @@
     <t>t06623</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06623/a06/</t>
+  </si>
+  <si>
     <t>全美戲院</t>
   </si>
   <si>
@@ -1523,6 +1748,9 @@
     <t>t06625</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06625/a06/</t>
+  </si>
+  <si>
     <t>麻豆戲院</t>
   </si>
   <si>
@@ -1544,6 +1772,9 @@
     <t>t06628</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06628/a06/</t>
+  </si>
+  <si>
     <t>台南仁德秀泰影城</t>
   </si>
   <si>
@@ -1565,6 +1796,9 @@
     <t>t07703</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07703/a07/</t>
+  </si>
+  <si>
     <t>高雄大遠百威秀影城</t>
   </si>
   <si>
@@ -1586,6 +1820,9 @@
     <t>t07702</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07702/a07/</t>
+  </si>
+  <si>
     <t>in89駁二電影院</t>
   </si>
   <si>
@@ -1607,6 +1844,9 @@
     <t>t07704</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07704/a07/</t>
+  </si>
+  <si>
     <t>高雄環球影城</t>
   </si>
   <si>
@@ -1628,6 +1868,9 @@
     <t>t07705</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07705/a07/</t>
+  </si>
+  <si>
     <t>國賓義大世界影城</t>
   </si>
   <si>
@@ -1646,6 +1889,9 @@
     <t>t07707</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07707/a07/</t>
+  </si>
+  <si>
     <t>高雄夢時代秀泰影城</t>
   </si>
   <si>
@@ -1667,6 +1913,9 @@
     <t>t07708</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07708/a07/</t>
+  </si>
+  <si>
     <t>國賓大魯閣草衙道影城</t>
   </si>
   <si>
@@ -1685,6 +1934,9 @@
     <t>t07712</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07712/a07/</t>
+  </si>
+  <si>
     <t>台鋁影城</t>
   </si>
   <si>
@@ -1706,6 +1958,9 @@
     <t>t07729</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07729/a07/</t>
+  </si>
+  <si>
     <t>高雄岡山秀泰</t>
   </si>
   <si>
@@ -1727,6 +1982,9 @@
     <t>t07726</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07726/a07/</t>
+  </si>
+  <si>
     <t>高雄市電影館</t>
   </si>
   <si>
@@ -1748,6 +2006,9 @@
     <t>t07727</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07727/a07/</t>
+  </si>
+  <si>
     <t>VR體感劇院</t>
   </si>
   <si>
@@ -1769,6 +2030,9 @@
     <t>t07728</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07728/a07/</t>
+  </si>
+  <si>
     <t>大立in89豪華影城</t>
   </si>
   <si>
@@ -1790,6 +2054,9 @@
     <t>t07730</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07730/a07/</t>
+  </si>
+  <si>
     <t>喜樂時代高雄總圖店</t>
   </si>
   <si>
@@ -1811,6 +2078,9 @@
     <t>t07731</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t07731/a07/</t>
+  </si>
+  <si>
     <t>內惟藝術中心</t>
   </si>
   <si>
@@ -1832,6 +2102,9 @@
     <t>t02g04</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t02g04/a01/</t>
+  </si>
+  <si>
     <t>基隆秀泰影城</t>
   </si>
   <si>
@@ -1856,6 +2129,9 @@
     <t>t03701</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03701/a37/</t>
+  </si>
+  <si>
     <t>頭份尚順威秀影城</t>
   </si>
   <si>
@@ -1877,6 +2153,9 @@
     <t>t04703</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04703/a47/</t>
+  </si>
+  <si>
     <t>員林影城</t>
   </si>
   <si>
@@ -1901,6 +2180,9 @@
     <t>t04501</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04501/a45/</t>
+  </si>
+  <si>
     <t>環球中華影城</t>
   </si>
   <si>
@@ -1925,6 +2207,9 @@
     <t>t04504</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04504/a45/</t>
+  </si>
+  <si>
     <t>雲林北港秀泰</t>
   </si>
   <si>
@@ -1946,6 +2231,9 @@
     <t>t04901</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04901/a49/</t>
+  </si>
+  <si>
     <t>南投戲院</t>
   </si>
   <si>
@@ -1970,6 +2258,9 @@
     <t>t04902</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t04902/a49/</t>
+  </si>
+  <si>
     <t>埔里山明影城</t>
   </si>
   <si>
@@ -1991,6 +2282,9 @@
     <t>t05502</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t05502/a05/</t>
+  </si>
+  <si>
     <t>嘉年華戲院</t>
   </si>
   <si>
@@ -2015,6 +2309,9 @@
     <t>t05504</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t05504/a05/</t>
+  </si>
+  <si>
     <t>嘉義秀泰影城</t>
   </si>
   <si>
@@ -2036,6 +2333,9 @@
     <t>t05505</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t05505/a05/</t>
+  </si>
+  <si>
     <t>嘉義in89豪華影城</t>
   </si>
   <si>
@@ -2057,6 +2357,9 @@
     <t>t03902</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03902/a39/</t>
+  </si>
+  <si>
     <t>宜蘭日新戲院</t>
   </si>
   <si>
@@ -2081,6 +2384,9 @@
     <t>t03904</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03904/a39/</t>
+  </si>
+  <si>
     <t>日新戲院-統一廳</t>
   </si>
   <si>
@@ -2102,6 +2408,9 @@
     <t>t03905</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03905/a39/</t>
+  </si>
+  <si>
     <t>新月豪華影城</t>
   </si>
   <si>
@@ -2123,6 +2432,9 @@
     <t>t03801</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03801/a38/</t>
+  </si>
+  <si>
     <t>花蓮秀泰影城</t>
   </si>
   <si>
@@ -2147,6 +2459,9 @@
     <t>t03803</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03803/a38/</t>
+  </si>
+  <si>
     <t>花蓮新天堂樂園威秀影城</t>
   </si>
   <si>
@@ -2165,6 +2480,9 @@
     <t>t03804</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t03804/a38/</t>
+  </si>
+  <si>
     <t>花蓮鐵道電影院</t>
   </si>
   <si>
@@ -2186,6 +2504,9 @@
     <t>t08902</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t08902/a89/</t>
+  </si>
+  <si>
     <t>台東秀泰影城</t>
   </si>
   <si>
@@ -2210,6 +2531,9 @@
     <t>t08701</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t08701/a87/</t>
+  </si>
+  <si>
     <t>中影屏東影城</t>
   </si>
   <si>
@@ -2234,6 +2558,9 @@
     <t>t08703</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t08703/a87/</t>
+  </si>
+  <si>
     <t>國賓屏東環球影城</t>
   </si>
   <si>
@@ -2252,6 +2579,9 @@
     <t>t06902</t>
   </si>
   <si>
+    <t>https://www.atmovies.com.tw/showtime/t06902/a69/</t>
+  </si>
+  <si>
     <t>in89澎湖影城</t>
   </si>
   <si>
@@ -2274,6 +2604,9 @@
   </si>
   <si>
     <t>t06801</t>
+  </si>
+  <si>
+    <t>https://www.atmovies.com.tw/showtime/t06801/a68/</t>
   </si>
   <si>
     <t>金獅影城</t>
@@ -2336,7 +2669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2376,4109 +2709,4436 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>24</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M17" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M18" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M19" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M20" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L21" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M21" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L22" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L24" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M24" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>15</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L27" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M28" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="J29" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L29" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M29" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L30" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M30" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L31" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M31" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="J32" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L32" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="J33" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L33" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L34" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>182</v>
+        <v>278</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="G35" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L35" t="s" s="0">
         <v>244</v>
       </c>
-      <c r="H35" t="s" s="0">
-        <v>245</v>
-      </c>
-      <c r="I35" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J35" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K35" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="L35" t="s" s="0">
-        <v>212</v>
+      <c r="M35" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="J36" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L36" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>182</v>
+        <v>294</v>
       </c>
       <c r="E37" t="s" s="0">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="J37" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L37" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="E38" t="s" s="0">
-        <v>263</v>
+        <v>210</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="J38" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L38" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M38" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>182</v>
+        <v>310</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="J39" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L39" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M39" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="J40" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L40" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M40" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>171</v>
+        <v>330</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="J41" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L41" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M41" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="J42" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L42" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M42" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="F43" t="s" s="0">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="J43" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L43" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M43" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="F44" t="s" s="0">
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J44" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L44" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M44" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>284</v>
+        <v>357</v>
       </c>
       <c r="E45" t="s" s="0">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="F45" t="s" s="0">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L45" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M45" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>284</v>
+        <v>364</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>320</v>
+        <v>367</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="J46" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L46" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M46" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>323</v>
+        <v>371</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F47" t="s" s="0">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L47" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M47" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E48" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="B48" t="s" s="0">
-        <v>328</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>329</v>
-      </c>
-      <c r="D48" t="s" s="0">
-        <v>284</v>
-      </c>
-      <c r="E48" t="s" s="0">
-        <v>330</v>
-      </c>
       <c r="F48" t="s" s="0">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>96</v>
+        <v>382</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L48" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M48" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>284</v>
+        <v>386</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="J49" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L49" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M49" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>284</v>
+        <v>394</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="J50" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L50" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M50" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>351</v>
+        <v>403</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L51" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M51" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>355</v>
+        <v>408</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>357</v>
+        <v>403</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L52" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M52" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>362</v>
+        <v>416</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="E53" t="s" s="0">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="F53" t="s" s="0">
-        <v>364</v>
+        <v>418</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>137</v>
+        <v>420</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="J53" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L53" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M53" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>366</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="E54" t="s" s="0">
-        <v>370</v>
+        <v>425</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>371</v>
+        <v>426</v>
       </c>
       <c r="G54" t="s" s="0">
-        <v>372</v>
+        <v>427</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>96</v>
+        <v>428</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="J54" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L54" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M54" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>374</v>
+        <v>430</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L55" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M55" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>369</v>
+        <v>439</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L56" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M56" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="E57" t="s" s="0">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="F57" t="s" s="0">
-        <v>389</v>
+        <v>447</v>
       </c>
       <c r="G57" t="s" s="0">
-        <v>390</v>
+        <v>448</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L57" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M57" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>369</v>
+        <v>453</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>396</v>
+        <v>455</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="J58" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L58" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M58" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>369</v>
+        <v>461</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>20</v>
+        <v>465</v>
       </c>
       <c r="J59" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L59" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M59" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>405</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>406</v>
+        <v>467</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>407</v>
+        <v>468</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="F60" t="s" s="0">
-        <v>409</v>
+        <v>470</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>410</v>
+        <v>471</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>411</v>
+        <v>472</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>20</v>
+        <v>473</v>
       </c>
       <c r="J60" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K60" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L60" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M60" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>413</v>
+        <v>475</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>414</v>
+        <v>476</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>369</v>
+        <v>477</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>416</v>
+        <v>478</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>417</v>
+        <v>479</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="J61" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K61" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L61" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M61" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>420</v>
+        <v>483</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>421</v>
+        <v>484</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>369</v>
+        <v>485</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F62" t="s" s="0">
-        <v>423</v>
+        <v>486</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>424</v>
+        <v>487</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>425</v>
+        <v>488</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>20</v>
+        <v>489</v>
       </c>
       <c r="J62" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K62" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L62" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M62" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>426</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>427</v>
+        <v>491</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>369</v>
+        <v>493</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>430</v>
+        <v>494</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>431</v>
+        <v>495</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>432</v>
+        <v>496</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>20</v>
+        <v>497</v>
       </c>
       <c r="J63" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K63" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L63" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M63" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>433</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>434</v>
+        <v>499</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>435</v>
+        <v>500</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>369</v>
+        <v>501</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F64" t="s" s="0">
-        <v>437</v>
+        <v>502</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>439</v>
+        <v>504</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>20</v>
+        <v>505</v>
       </c>
       <c r="J64" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K64" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L64" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M64" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>441</v>
+        <v>507</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>442</v>
+        <v>508</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>369</v>
+        <v>509</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>444</v>
+        <v>510</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>445</v>
+        <v>511</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>446</v>
+        <v>512</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>20</v>
+        <v>513</v>
       </c>
       <c r="J65" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K65" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L65" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M65" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>447</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>448</v>
+        <v>515</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>449</v>
+        <v>516</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>369</v>
+        <v>517</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>451</v>
+        <v>518</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>452</v>
+        <v>519</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>453</v>
+        <v>520</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>20</v>
+        <v>521</v>
       </c>
       <c r="J66" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K66" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L66" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M66" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>369</v>
+        <v>525</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>458</v>
+        <v>526</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>460</v>
+        <v>528</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>20</v>
+        <v>529</v>
       </c>
       <c r="J67" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K67" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L67" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M67" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>462</v>
+        <v>531</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>464</v>
+        <v>533</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>465</v>
+        <v>534</v>
       </c>
       <c r="F68" t="s" s="0">
-        <v>466</v>
+        <v>535</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>467</v>
+        <v>536</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>96</v>
+        <v>537</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="J68" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K68" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L68" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M68" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>468</v>
+        <v>538</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>469</v>
+        <v>539</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>464</v>
+        <v>541</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>471</v>
+        <v>534</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>472</v>
+        <v>542</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>473</v>
+        <v>543</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>19</v>
+        <v>544</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K69" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L69" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M69" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>474</v>
+        <v>545</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>475</v>
+        <v>546</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>464</v>
+        <v>548</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>477</v>
+        <v>534</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>478</v>
+        <v>549</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>19</v>
+        <v>551</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K70" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L70" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M70" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>482</v>
+        <v>554</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>464</v>
+        <v>555</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>484</v>
+        <v>556</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>485</v>
+        <v>557</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K71" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L71" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M71" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>486</v>
+        <v>559</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>488</v>
+        <v>561</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>464</v>
+        <v>562</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="F72" t="s" s="0">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>491</v>
+        <v>564</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>492</v>
+        <v>565</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>20</v>
+        <v>566</v>
       </c>
       <c r="J72" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K72" t="s" s="0">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="L72" t="s" s="0">
-        <v>212</v>
+        <v>244</v>
+      </c>
+      <c r="M72" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>493</v>
+        <v>567</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>494</v>
+        <v>568</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>495</v>
+        <v>569</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>464</v>
+        <v>570</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>496</v>
+        <v>534</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>497</v>
+        <v>571</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>498</v>
+        <v>572</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>499</v>
+        <v>573</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>20</v>
+        <v>574</v>
       </c>
       <c r="J73" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K73" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L73" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M73" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>501</v>
+        <v>576</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>502</v>
+        <v>577</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>503</v>
+        <v>578</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>464</v>
+        <v>579</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>505</v>
+        <v>580</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>506</v>
+        <v>581</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>507</v>
+        <v>582</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>20</v>
+        <v>583</v>
       </c>
       <c r="J74" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K74" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L74" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M74" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>508</v>
+        <v>584</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>509</v>
+        <v>585</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>510</v>
+        <v>586</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>464</v>
+        <v>587</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>512</v>
+        <v>588</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>513</v>
+        <v>589</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>20</v>
+        <v>591</v>
       </c>
       <c r="J75" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K75" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L75" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M75" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>515</v>
+        <v>592</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>516</v>
+        <v>593</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>517</v>
+        <v>594</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>518</v>
+        <v>595</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>519</v>
+        <v>596</v>
       </c>
       <c r="F76" t="s" s="0">
-        <v>520</v>
+        <v>597</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>521</v>
+        <v>598</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>19</v>
+        <v>599</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K76" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L76" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M76" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>522</v>
+        <v>600</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>523</v>
+        <v>601</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>524</v>
+        <v>602</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>518</v>
+        <v>603</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>525</v>
+        <v>596</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>526</v>
+        <v>604</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>527</v>
+        <v>605</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>528</v>
+        <v>606</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>20</v>
+        <v>607</v>
       </c>
       <c r="J77" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K77" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L77" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M77" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>530</v>
+        <v>609</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>531</v>
+        <v>610</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>518</v>
+        <v>611</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>532</v>
+        <v>596</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>533</v>
+        <v>612</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>534</v>
+        <v>613</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>20</v>
+        <v>615</v>
       </c>
       <c r="J78" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K78" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L78" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M78" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>536</v>
+        <v>616</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>537</v>
+        <v>617</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>538</v>
+        <v>618</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>518</v>
+        <v>619</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>541</v>
+        <v>621</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J79" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K79" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L79" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M79" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>542</v>
+        <v>623</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>543</v>
+        <v>624</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>544</v>
+        <v>625</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>518</v>
+        <v>626</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>545</v>
+        <v>596</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>546</v>
+        <v>627</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>547</v>
+        <v>628</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>548</v>
+        <v>629</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>20</v>
+        <v>630</v>
       </c>
       <c r="J80" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K80" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L80" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M80" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>549</v>
+        <v>631</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>550</v>
+        <v>632</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>551</v>
+        <v>633</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>518</v>
+        <v>634</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="F81" t="s" s="0">
-        <v>553</v>
+        <v>635</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>554</v>
+        <v>636</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J81" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K81" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L81" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M81" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>555</v>
+        <v>638</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>556</v>
+        <v>639</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>557</v>
+        <v>640</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>518</v>
+        <v>641</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>559</v>
+        <v>642</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>560</v>
+        <v>643</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>561</v>
+        <v>644</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>20</v>
+        <v>645</v>
       </c>
       <c r="J82" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K82" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L82" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M82" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>562</v>
+        <v>646</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>563</v>
+        <v>647</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>518</v>
+        <v>649</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>565</v>
+        <v>596</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>566</v>
+        <v>650</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>568</v>
+        <v>652</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>20</v>
+        <v>653</v>
       </c>
       <c r="J83" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L83" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M83" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>569</v>
+        <v>654</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>570</v>
+        <v>655</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>571</v>
+        <v>656</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>518</v>
+        <v>657</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="F84" t="s" s="0">
-        <v>573</v>
+        <v>658</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>574</v>
+        <v>659</v>
       </c>
       <c r="H84" t="s" s="0">
+        <v>660</v>
+      </c>
+      <c r="I84" t="s" s="0">
+        <v>661</v>
+      </c>
+      <c r="J84" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K84" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L84" t="s" s="0">
         <v>575</v>
       </c>
-      <c r="I84" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J84" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K84" t="s" s="0">
-        <v>500</v>
-      </c>
-      <c r="L84" t="s" s="0">
-        <v>500</v>
+      <c r="M84" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>576</v>
+        <v>662</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>577</v>
+        <v>663</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>578</v>
+        <v>664</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>518</v>
+        <v>665</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>580</v>
+        <v>666</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>581</v>
+        <v>667</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>20</v>
+        <v>669</v>
       </c>
       <c r="J85" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K85" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L85" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M85" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>583</v>
+        <v>670</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>584</v>
+        <v>671</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>585</v>
+        <v>672</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>518</v>
+        <v>673</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>587</v>
+        <v>674</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>588</v>
+        <v>675</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>589</v>
+        <v>676</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>20</v>
+        <v>677</v>
       </c>
       <c r="J86" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K86" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L86" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M86" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>590</v>
+        <v>678</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>592</v>
+        <v>680</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>518</v>
+        <v>681</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>594</v>
+        <v>682</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>595</v>
+        <v>683</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>596</v>
+        <v>684</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>20</v>
+        <v>685</v>
       </c>
       <c r="J87" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K87" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L87" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M87" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>597</v>
+        <v>686</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>598</v>
+        <v>687</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>518</v>
+        <v>689</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F88" t="s" s="0">
-        <v>601</v>
+        <v>690</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>602</v>
+        <v>691</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>603</v>
+        <v>692</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>20</v>
+        <v>693</v>
       </c>
       <c r="J88" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K88" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L88" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M88" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>604</v>
+        <v>694</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>605</v>
+        <v>695</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>606</v>
+        <v>696</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>607</v>
+        <v>697</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>608</v>
+        <v>698</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>609</v>
+        <v>699</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>610</v>
+        <v>700</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>611</v>
+        <v>701</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>20</v>
+        <v>702</v>
       </c>
       <c r="J89" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K89" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L89" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M89" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>612</v>
+        <v>703</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>613</v>
+        <v>704</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>614</v>
+        <v>705</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>615</v>
+        <v>706</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>616</v>
+        <v>707</v>
       </c>
       <c r="F90" t="s" s="0">
-        <v>617</v>
+        <v>708</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>618</v>
+        <v>709</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>19</v>
+        <v>710</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K90" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L90" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M90" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>619</v>
+        <v>711</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>620</v>
+        <v>712</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>621</v>
+        <v>713</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>622</v>
+        <v>714</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>623</v>
+        <v>715</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>624</v>
+        <v>716</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>625</v>
+        <v>717</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>626</v>
+        <v>718</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>20</v>
+        <v>719</v>
       </c>
       <c r="J91" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K91" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L91" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M91" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>627</v>
+        <v>720</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>628</v>
+        <v>721</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>629</v>
+        <v>722</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>630</v>
+        <v>723</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>631</v>
+        <v>724</v>
       </c>
       <c r="F92" t="s" s="0">
-        <v>632</v>
+        <v>725</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>633</v>
+        <v>726</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>634</v>
+        <v>727</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>20</v>
+        <v>728</v>
       </c>
       <c r="J92" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K92" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L92" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M92" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>635</v>
+        <v>729</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>636</v>
+        <v>730</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>637</v>
+        <v>731</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>630</v>
+        <v>732</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>639</v>
+        <v>733</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>641</v>
+        <v>735</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>20</v>
+        <v>736</v>
       </c>
       <c r="J93" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K93" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L93" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M93" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>642</v>
+        <v>737</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>643</v>
+        <v>738</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>645</v>
+        <v>740</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>646</v>
+        <v>741</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>647</v>
+        <v>742</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>648</v>
+        <v>743</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>649</v>
+        <v>744</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>20</v>
+        <v>745</v>
       </c>
       <c r="J94" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K94" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L94" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M94" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>650</v>
+        <v>746</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>651</v>
+        <v>747</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>652</v>
+        <v>748</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>645</v>
+        <v>749</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>653</v>
+        <v>741</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>654</v>
+        <v>750</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>655</v>
+        <v>751</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>656</v>
+        <v>752</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>20</v>
+        <v>753</v>
       </c>
       <c r="J95" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K95" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L95" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M95" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>657</v>
+        <v>754</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>658</v>
+        <v>755</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>659</v>
+        <v>756</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>660</v>
+        <v>757</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>661</v>
+        <v>758</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>662</v>
+        <v>759</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>663</v>
+        <v>760</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>664</v>
+        <v>761</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>20</v>
+        <v>762</v>
       </c>
       <c r="J96" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K96" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L96" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M96" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>665</v>
+        <v>763</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>666</v>
+        <v>764</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>667</v>
+        <v>765</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>660</v>
+        <v>766</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>668</v>
+        <v>758</v>
       </c>
       <c r="F97" t="s" s="0">
-        <v>669</v>
+        <v>767</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>670</v>
+        <v>768</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>671</v>
+        <v>769</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>20</v>
+        <v>770</v>
       </c>
       <c r="J97" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L97" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M97" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>672</v>
+        <v>771</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>673</v>
+        <v>772</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>674</v>
+        <v>773</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>675</v>
+        <v>758</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>676</v>
+        <v>775</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>677</v>
+        <v>776</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>678</v>
+        <v>777</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>20</v>
+        <v>778</v>
       </c>
       <c r="J98" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L98" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M98" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>679</v>
+        <v>779</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>680</v>
+        <v>780</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>681</v>
+        <v>781</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>682</v>
+        <v>782</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>683</v>
+        <v>783</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>684</v>
+        <v>784</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>685</v>
+        <v>785</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>686</v>
+        <v>786</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>20</v>
+        <v>787</v>
       </c>
       <c r="J99" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L99" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M99" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>687</v>
+        <v>788</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>688</v>
+        <v>789</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>689</v>
+        <v>790</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>682</v>
+        <v>791</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>690</v>
+        <v>783</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>691</v>
+        <v>792</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>692</v>
+        <v>793</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>693</v>
+        <v>794</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>20</v>
+        <v>795</v>
       </c>
       <c r="J100" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L100" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M100" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>694</v>
+        <v>796</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>695</v>
+        <v>797</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>696</v>
+        <v>798</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>682</v>
+        <v>799</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>697</v>
+        <v>783</v>
       </c>
       <c r="F101" t="s" s="0">
-        <v>698</v>
+        <v>800</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>699</v>
+        <v>801</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>700</v>
+        <v>802</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>20</v>
+        <v>803</v>
       </c>
       <c r="J101" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L101" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M101" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>701</v>
+        <v>804</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>702</v>
+        <v>805</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>703</v>
+        <v>806</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>704</v>
+        <v>807</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>705</v>
+        <v>808</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>706</v>
+        <v>809</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>707</v>
+        <v>810</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>708</v>
+        <v>811</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>20</v>
+        <v>812</v>
       </c>
       <c r="J102" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L102" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M102" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>709</v>
+        <v>813</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>710</v>
+        <v>814</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>711</v>
+        <v>815</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>704</v>
+        <v>816</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>712</v>
+        <v>808</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>713</v>
+        <v>817</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>714</v>
+        <v>818</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>19</v>
+        <v>819</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J103" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L103" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M103" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>715</v>
+        <v>820</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>716</v>
+        <v>821</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>717</v>
+        <v>822</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>704</v>
+        <v>823</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>718</v>
+        <v>808</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>719</v>
+        <v>824</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>720</v>
+        <v>825</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>721</v>
+        <v>826</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>20</v>
+        <v>827</v>
       </c>
       <c r="J104" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L104" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M104" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>722</v>
+        <v>828</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>723</v>
+        <v>829</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>724</v>
+        <v>830</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>725</v>
+        <v>831</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>726</v>
+        <v>832</v>
       </c>
       <c r="F105" t="s" s="0">
-        <v>727</v>
+        <v>833</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>728</v>
+        <v>834</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>729</v>
+        <v>835</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>20</v>
+        <v>836</v>
       </c>
       <c r="J105" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K105" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L105" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M105" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>730</v>
+        <v>837</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>731</v>
+        <v>838</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>732</v>
+        <v>839</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>733</v>
+        <v>840</v>
       </c>
       <c r="E106" t="s" s="0">
-        <v>734</v>
+        <v>841</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>735</v>
+        <v>842</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>736</v>
+        <v>843</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>737</v>
+        <v>844</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>20</v>
+        <v>845</v>
       </c>
       <c r="J106" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K106" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L106" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M106" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>738</v>
+        <v>846</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>739</v>
+        <v>847</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>740</v>
+        <v>848</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>733</v>
+        <v>849</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>741</v>
+        <v>841</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>742</v>
+        <v>850</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>743</v>
+        <v>851</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>82</v>
+        <v>852</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J107" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K107" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L107" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M107" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>744</v>
+        <v>853</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>745</v>
+        <v>854</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>746</v>
+        <v>855</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>747</v>
+        <v>856</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>748</v>
+        <v>857</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>749</v>
+        <v>858</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>750</v>
+        <v>859</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>751</v>
+        <v>860</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>20</v>
+        <v>861</v>
       </c>
       <c r="J108" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K108" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L108" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M108" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>752</v>
+        <v>862</v>
       </c>
       <c r="B109" t="s" s="0">
-        <v>753</v>
+        <v>863</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>754</v>
+        <v>864</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>755</v>
+        <v>865</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>756</v>
+        <v>866</v>
       </c>
       <c r="F109" t="s" s="0">
-        <v>757</v>
+        <v>867</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>758</v>
+        <v>868</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>759</v>
+        <v>869</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>20</v>
+        <v>870</v>
       </c>
       <c r="J109" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K109" t="s" s="0">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="L109" t="s" s="0">
-        <v>500</v>
+        <v>575</v>
+      </c>
+      <c r="M109" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
